--- a/docs/design_guideline_document.xlsx
+++ b/docs/design_guideline_document.xlsx
@@ -323,7 +323,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>信頼感 / 伴走感 / 俊敏性</t>
+          <t>信頼感 / 親しみやすさ / 行動しやすさ</t>
         </is>
       </c>
     </row>
@@ -335,7 +335,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>M PLUS Rounded 1c（補助: M PLUS 1p）</t>
+          <t>Fredoka（見出し） / M PLUS Rounded 1c（本文）</t>
         </is>
       </c>
     </row>
@@ -347,7 +347,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>#1D4ED8</t>
+          <t>#FF8FB1</t>
         </is>
       </c>
     </row>
@@ -399,132 +399,132 @@
     <row r="2" ht="15" customHeight="1" s="4">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>メインカラー</t>
+          <t>メインカラー（--brand）</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>#1D4ED8</t>
+          <t>#FF8FB1</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>ヘッダー・見出し</t>
+          <t>主要CTA、強調ラベル</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>信頼・誠実・安心の心理効果</t>
+          <t>親しみと行動喚起</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="4">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>サブカラー</t>
+          <t>メイン濃色（--brand-dark）</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>#0EA5A4</t>
+          <t>#FF6E9A</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>補助ボタン・ステップ</t>
+          <t>主要CTAホバー</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>調和・回復・伴走感</t>
+          <t>状態変化の明確化</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>アクセントカラー</t>
+          <t>サブカラー（--accent）</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>#F59E0B</t>
+          <t>#8C6EE6</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>CTA・注意喚起</t>
+          <t>統計値の強調</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>行動促進・視認性向上</t>
+          <t>視線誘導の補助</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="4">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>背景色</t>
+          <t>アクセント（--mint）</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>#F8FAFC</t>
+          <t>#C9F7EF</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>ページ背景</t>
+          <t>補助背景</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>圧迫感軽減・可読性確保</t>
+          <t>安心感の演出</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="4">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>テキスト（メイン）</t>
+          <t>背景色（--bg）</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>#0F172A</t>
+          <t>#FFF9FB</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>ページ背景</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>高コントラスト</t>
+          <t>高明度で疲れにくい</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="4">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>テキスト（サブ）</t>
+          <t>テキスト（--text / --muted）</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>#64748B</t>
+          <t>#4A2D3C / #7A6170</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>補助情報</t>
+          <t>本文 / 補助情報</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>情報優先度の分離</t>
+          <t>可読性と情報優先度の分離</t>
         </is>
       </c>
     </row>
@@ -588,17 +588,17 @@
     <row r="2" ht="15" customHeight="1" s="4">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>h1</t>
+          <t>h1（大見出し）</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>M PLUS Rounded 1c</t>
+          <t>Fredoka</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>40px</t>
+          <t>30px</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -608,61 +608,61 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0.02em</t>
+          <t>0.01em</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="4">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>h2（中見出し）</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>M PLUS Rounded 1c</t>
+          <t>Fredoka</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>30px</t>
+          <t>22px</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>600</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>約1.3</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>0.015em</t>
+          <t>0em</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>h3</t>
+          <t>h3（小見出し）</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>M PLUS Rounded 1c</t>
+          <t>Fredoka</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>22px</t>
+          <t>16px</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -672,12 +672,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>約1.4</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0.01em</t>
+          <t>0em</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>0.01em</t>
+          <t>0em</t>
         </is>
       </c>
     </row>
@@ -731,17 +731,17 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>600</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0.015em</t>
+          <t>0em</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>700</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>約1.2</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>0.02em</t>
+          <t>0em</t>
         </is>
       </c>
     </row>
@@ -824,24 +824,24 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>角丸14px / primary-secondary-danger</t>
+          <t>pill型 / primary-secondary（角丸999px）</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>hover / active</t>
+          <t>hover</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="4">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>フォーム</t>
+          <t>フォーム要素</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>入力・select・textarea・checkbox・radio・toggle</t>
+          <t>text・select・textarea・checkbox・radio・toggle</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -853,51 +853,51 @@
     <row r="4" ht="15" customHeight="1" s="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>カード</t>
+          <t>ナビゲーション</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>画像+タイトル+テキスト+ボタン</t>
+          <t>sticky header / hamburger / drawer nav</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>hover elevation</t>
+          <t>mobile/pc切替</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="4">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>テーブル</t>
+          <t>カード・バナー・統計</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>ヘッダー付き / ストライプ行</t>
+          <t>card・image-card・stat・value-banner</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>hover row</t>
+          <t>responsive</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="4">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>アラート</t>
+          <t>テーブル・アラート</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>info / success / warning / error</t>
+          <t>price-table / info-success-warning-error</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>色分け</t>
+          <t>状態色分け</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>1200px（92vw）</t>
+          <t>width: 82vw / max-width: 960px</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>PC:12 / Tab:8 / SP:4 カラム</t>
+          <t>基本1カラム。PC: hero 1.2fr/0.8fr, cards 3列</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>PC/Tab:24px, SP:16px</t>
+          <t>gap目安: hero 24px / card 22px</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>PC:64px / Tab:48px / SP:32px</t>
+          <t>--space-section: 36px</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>8pxスケール（8/12/16/24/32）</t>
+          <t>--space-block: 22px / --space-tight: 14px</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>入力10px / ボタン14px / カード14px / モーダル16px</t>
+          <t>カード26px / 画像18-20px / ボタン999px</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>0 8px 20px rgba(15,23,42,.05) 等</t>
+          <t>0 10px 20px rgba(221,136,170,0.12)</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>PC:&gt;=1024 / Tab:768-1023 / SP:&lt;=767</t>
+          <t>768px（未満SP / 以上PC）</t>
         </is>
       </c>
     </row>
